--- a/exports/488_san-andres.xlsx
+++ b/exports/488_san-andres.xlsx
@@ -4581,45 +4581,45 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>60369313</t>
+          <t>20982401</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>HERNAN</t>
+          <t>TEODORA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18/12/2002</t>
+          <t>14/12/1962</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>20/02/2012</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,45 +4644,45 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20982401</t>
+          <t>43120883</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>PERALES</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TEODORA</t>
+          <t>EDWIN IVAN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14/12/1962</t>
+          <t>14/07/1985</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>43120883</t>
+          <t>46240896</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EDWIN IVAN</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4731,11 +4731,11 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14/07/1985</t>
+          <t>14/09/1989</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4770,22 +4770,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>46240896</t>
+          <t>40537496</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>ESPEJO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PERALES</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>JORGE LUIS</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4794,11 +4794,11 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14/09/1989</t>
+          <t>05/04/1979</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,22 +4833,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>40537496</t>
+          <t>91930187</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ESPEJO</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>OSORIO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>JORGE LUIS</t>
+          <t>JHAYR ALDAHIR ADRIEL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,16 +4857,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>05/04/1979</t>
+          <t>14/07/2020</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>73091283</t>
+          <t>20991423</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ESPIRITU</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>RONALDO ROBERTO</t>
+          <t>APARICIO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>06/08/1998</t>
+          <t>12/12/1966</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>09/02/2015</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,22 +4959,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>91930187</t>
+          <t>61507200</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OSORIO</t>
+          <t>CAINICELA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>JHAYR ALDAHIR ADRIEL</t>
+          <t>JEFERSON FRANDUKS</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4983,16 +4983,16 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14/07/2020</t>
+          <t>18/04/2009</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,45 +5022,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20991423</t>
+          <t>61634660</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>GUTARRA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>APARICIO</t>
+          <t>BRILLIT MAYELY</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>12/12/1966</t>
+          <t>03/01/2009</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>09/02/2015</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,7 +5085,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>61634660</t>
+          <t>81479837</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5100,30 +5100,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BRILLIT MAYELY</t>
+          <t>BRAYAN SMITH</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>03/01/2009</t>
+          <t>11/07/2015</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>19/11/2015</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,7 +5148,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>81479837</t>
+          <t>41715866</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CARHUAMACA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BRAYAN SMITH</t>
+          <t>VALENTIN</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>11/07/2015</t>
+          <t>12/06/1981</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>19/11/2015</t>
+          <t>21/07/2016</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,22 +5211,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>41715866</t>
+          <t>77904813</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GUTARRA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CARHUAMACA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VALENTIN</t>
+          <t>VICTOR RODOLFO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>12/06/1981</t>
+          <t>24/02/2001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>21/07/2016</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,22 +5274,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>77904813</t>
+          <t>20962206</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VICTOR RODOLFO</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>24/02/2001</t>
+          <t>27/08/1946</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,22 +5337,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20962206</t>
+          <t>47867880</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>JONAS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5361,16 +5361,16 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>27/08/1946</t>
+          <t>25/05/1992</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>11/09/2020</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>47867880</t>
+          <t>77213330</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5415,20 +5415,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>JONAS</t>
+          <t>FLOR KELLY</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>25/05/1992</t>
+          <t>26/06/1995</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>11/09/2020</t>
+          <t>21/08/2012</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,7 +5463,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>77213330</t>
+          <t>20047153</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5473,25 +5473,25 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>FLOR KELLY</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>26/06/1995</t>
+          <t>08/12/1971</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>21/08/2012</t>
+          <t>24/05/2016</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,35 +5526,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20047153</t>
+          <t>80634083</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>INOCENTE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>PATRICIA MARGOT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>08/12/1971</t>
+          <t>27/10/1978</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>24/05/2016</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>80634083</t>
+          <t>79213733</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>INOCENTE</t>
+          <t>LAPA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PATRICIA MARGOT</t>
+          <t>TAYRA DANNA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5613,21 +5613,21 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>27/10/1978</t>
+          <t>28/05/2015</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,22 +5652,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>79213733</t>
+          <t>20420557</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LAPA</t>
+          <t>LAUREANO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>MANTARI</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TAYRA DANNA</t>
+          <t>ELA MARCEA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5676,21 +5676,21 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>28/05/2015</t>
+          <t>26/10/1965</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20420557</t>
+          <t>20990369</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LAUREANO</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MANTARI</t>
+          <t>CAYSAHUANA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ELA MARCEA</t>
+          <t>CATALINA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,11 +5739,11 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>26/10/1965</t>
+          <t>25/11/1949</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>28/11/2014</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20990369</t>
+          <t>48998854</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5788,25 +5788,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CAYSAHUANA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CATALINA</t>
+          <t>PEDRO PABLO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>25/11/1949</t>
+          <t>29/06/1963</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>28/11/2014</t>
+          <t>14/09/2020</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,35 +5841,35 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>48998854</t>
+          <t>20968366</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>LIMAS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CAMPOS DE CAMARGO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PEDRO PABLO</t>
+          <t>TEOFILA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>29/06/1963</t>
+          <t>02/09/1934</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>14/09/2020</t>
+          <t>01/09/2016</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,45 +5904,45 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20968366</t>
+          <t>46371234</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LIMAS</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CAMPOS DE CAMARGO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TEOFILA</t>
+          <t>CEFERINO ARMANDO</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>02/09/1934</t>
+          <t>23/02/1989</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>01/09/2016</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,22 +5967,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>46371234</t>
+          <t>61697344</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>MAGUIÑA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CEFERINO ARMANDO</t>
+          <t>JHOVANY ROLY</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5991,21 +5991,21 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23/02/1989</t>
+          <t>27/05/2010</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,7 +6030,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>61697344</t>
+          <t>81479820</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6045,30 +6045,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>JHOVANY ROLY</t>
+          <t>MARIANA YOMARA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>27/05/2010</t>
+          <t>29/03/2015</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>29/05/2020</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,22 +6093,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>81479820</t>
+          <t>72178504</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MAGUIÑA</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MARIANA YOMARA</t>
+          <t>KHERLY JOHANA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,16 +6117,16 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>29/03/2015</t>
+          <t>16/05/2000</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>29/05/2020</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,45 +6156,45 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>72178504</t>
+          <t>73668062</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>MARAVI</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>VALTOP</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>KHERLY JOHANA</t>
+          <t>HILSER ELMER</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>16/05/2000</t>
+          <t>14/05/1994</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>27/11/2020</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>73668062</t>
+          <t>45045846</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MARAVI</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VALTOP</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>HILSER ELMER</t>
+          <t>OSCAR BENITO</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6243,11 +6243,11 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>14/05/1994</t>
+          <t>23/02/1988</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>27/11/2020</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,7 +6282,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>45045846</t>
+          <t>80349247</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>OSCAR BENITO</t>
+          <t>NOE ISAIAS</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6306,11 +6306,11 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>23/02/1988</t>
+          <t>21/07/1979</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,22 +6345,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>80349247</t>
+          <t>48484599</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MOYA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NOE ISAIAS</t>
+          <t>DAVID ANGEL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6369,11 +6369,11 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>21/07/1979</t>
+          <t>16/01/1994</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>28/03/2013</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,7 +6408,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>48484599</t>
+          <t>46967694</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6418,25 +6418,25 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>DAVID ANGEL</t>
+          <t>LUCIANA SUSANA</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>16/01/1994</t>
+          <t>30/05/1991</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>28/03/2013</t>
+          <t>04/05/2012</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,7 +6471,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>46967694</t>
+          <t>48759111</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LUCIANA SUSANA</t>
+          <t>EDITH</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6495,11 +6495,11 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>30/05/1991</t>
+          <t>09/10/1995</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>04/05/2012</t>
+          <t>19/08/2015</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>48759111</t>
+          <t>73668026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MOYA</t>
+          <t>PALACIOS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>EDITH</t>
+          <t>ZANDRA KARINA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>09/10/1995</t>
+          <t>18/09/1997</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>19/08/2015</t>
+          <t>19/03/2024</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,7 +6597,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>73668026</t>
+          <t>21013692</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6607,35 +6607,35 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>PORTOCARRERO</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ZANDRA KARINA</t>
+          <t>MARIO</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>18/09/1997</t>
+          <t>13/11/1977</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>19/03/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,7 +6660,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>21013692</t>
+          <t>20998003</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PORTOCARRERO</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>MARIO</t>
+          <t>TEODORO</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6684,16 +6684,16 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>13/11/1977</t>
+          <t>03/09/1965</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6723,22 +6723,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20998003</t>
+          <t>60369342</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PALACIOS</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SALOME</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>TEODORO</t>
+          <t>YAMIR FERNANDO</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,21 +6747,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>03/09/1965</t>
+          <t>18/05/2008</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,22 +6786,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>60369342</t>
+          <t>48638943</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>PATIÑO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>YAMIR FERNANDO</t>
+          <t>AMERICO</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6810,21 +6810,21 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>18/05/2008</t>
+          <t>22/10/1995</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,45 +6849,45 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>48638943</t>
+          <t>61282644</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PATIÑO</t>
+          <t>PAYANO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>LEVANO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AMERICO</t>
+          <t>ALEXANDRA CELINE</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>22/10/1995</t>
+          <t>31/01/2008</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,35 +6912,35 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>61282644</t>
+          <t>77145038</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PAYANO</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LEVANO</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ALEXANDRA CELINE</t>
+          <t>EFRAIN LIZANDRO</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>31/01/2008</t>
+          <t>25/06/2000</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,40 +6975,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>77145038</t>
+          <t>71957554</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>MONTALGO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>EFRAIN LIZANDRO</t>
+          <t>NELY JHENY</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>25/06/2000</t>
+          <t>18/10/1995</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,35 +7038,35 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>71957554</t>
+          <t>48096106</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MONTALGO</t>
+          <t>AVENIO</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NELY JHENY</t>
+          <t>ALEX LENIN</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>18/10/1995</t>
+          <t>24/01/1994</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>05/12/2013</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,7 +7101,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>48096106</t>
+          <t>78212853</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7111,30 +7111,30 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AVENIO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ALEX LENIN</t>
+          <t>DAYANA SAMIRA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>24/01/1994</t>
+          <t>11/07/2013</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7164,45 +7164,45 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>78212853</t>
+          <t>44931859</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>QUINTANILLA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>PARRAGA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DAYANA SAMIRA</t>
+          <t>MARINO LORENZO</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>11/07/2013</t>
+          <t>21/07/1987</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>05/12/2013</t>
+          <t>21/05/2021</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,22 +7227,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>44931859</t>
+          <t>20994095</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>QUINTANILLA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PARRAGA</t>
+          <t>ALIAGA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MARINO LORENZO</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7251,11 +7251,11 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>21/07/1987</t>
+          <t>03/01/1971</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>21/05/2021</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>20994095</t>
+          <t>42898832</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ALIAGA</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>MAXIMO JUAN</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>03/01/1971</t>
+          <t>27/03/1985</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>14/09/2020</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,7 +7353,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>42898832</t>
+          <t>48118279</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7363,25 +7363,25 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>MAXIMO JUAN</t>
+          <t>CELIA</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>27/03/1985</t>
+          <t>05/08/1990</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>14/09/2020</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,7 +7416,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>48118279</t>
+          <t>19963519</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>PASTRANA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CELIA</t>
+          <t>ANTONIA</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,11 +7440,11 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>05/08/1990</t>
+          <t>12/06/1968</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>14/10/2016</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,35 +7479,35 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>19963519</t>
+          <t>47788809</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PASTRANA</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ANTONIA</t>
+          <t>BASILIO</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>12/06/1968</t>
+          <t>13/04/1993</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>14/10/2016</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,45 +7542,45 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>47788809</t>
+          <t>20416033</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>BASILIO</t>
+          <t>PAULINA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>13/04/1993</t>
+          <t>04/05/1956</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,45 +7605,45 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>20416033</t>
+          <t>77498212</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>PAULINA</t>
+          <t>EMERSON WILLIAM</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>04/05/1956</t>
+          <t>24/10/1998</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,22 +7668,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>77498212</t>
+          <t>61697345</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EMERSON WILLIAM</t>
+          <t>ARTUR JHAIR</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,11 +7692,11 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>24/10/1998</t>
+          <t>17/01/2008</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,7 +7731,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>61697345</t>
+          <t>80846521</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ARTUR JHAIR</t>
+          <t>DANILO JOSSAFAT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>17/01/2008</t>
+          <t>13/09/2012</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>05/07/2013</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,7 +7794,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>80846521</t>
+          <t>81479855</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7809,25 +7809,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DANILO JOSSAFAT</t>
+          <t>ARELI TAMARA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>13/09/2012</t>
+          <t>15/10/2015</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>05/07/2013</t>
+          <t>19/04/2016</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,7 +7857,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>81479855</t>
+          <t>93360444</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7872,20 +7872,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ARELI TAMARA</t>
+          <t>ABDIAS OTONIEL</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>15/10/2015</t>
+          <t>25/04/2023</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>19/04/2016</t>
+          <t>26/07/2023</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,7 +7920,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>93360444</t>
+          <t>48893189</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ABDIAS OTONIEL</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7944,21 +7944,21 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>25/04/2023</t>
+          <t>17/07/1965</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>26/07/2023</t>
+          <t>27/10/2015</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,7 +7983,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>48893189</t>
+          <t>80064918</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>MARCIAL</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8007,21 +8007,21 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>17/07/1965</t>
+          <t>28/09/1977</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>27/10/2015</t>
+          <t>15/02/2012</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,7 +8046,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>80064918</t>
+          <t>42797175</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>MARCIAL</t>
+          <t>SAMUEL</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8070,11 +8070,11 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>28/09/1977</t>
+          <t>06/12/1984</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>15/02/2012</t>
+          <t>10/05/2016</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,22 +8109,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>42797175</t>
+          <t>46811206</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>POMA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SAMUEL</t>
+          <t>CUPERTINO</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8133,11 +8133,11 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>06/12/1984</t>
+          <t>31/12/1981</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>10/05/2016</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,45 +8172,45 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>46811206</t>
+          <t>61055413</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>RONCAL</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>POMA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>CUPERTINO</t>
+          <t>MARIANGELA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>31/12/1981</t>
+          <t>05/06/2007</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>07/02/2023</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,22 +8235,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>61055413</t>
+          <t>19959000</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RONCAL</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>MARIANGELA</t>
+          <t>ANA BRIGIDA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8259,21 +8259,21 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>05/06/2007</t>
+          <t>01/02/1961</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>07/02/2023</t>
+          <t>27/07/2016</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>19959000</t>
+          <t>20997885</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ANA BRIGIDA</t>
+          <t>ADELAIDA GENOVEBA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,11 +8322,11 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>01/02/1961</t>
+          <t>30/11/1956</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>27/07/2016</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,22 +8361,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>20997885</t>
+          <t>47441568</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SALOME</t>
+          <t>SALVATIERRA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>HUAYRA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ADELAIDA GENOVEBA</t>
+          <t>PAULINA</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8385,21 +8385,21 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>30/11/1956</t>
+          <t>22/06/1986</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>08/02/2012</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,22 +8424,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>47441568</t>
+          <t>45889751</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SALVATIERRA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>HUAYRA</t>
+          <t>ARZAPALO</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>PAULINA</t>
+          <t>KARINA ROSMERY</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8448,11 +8448,11 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>22/06/1986</t>
+          <t>02/12/1984</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>08/02/2012</t>
+          <t>21/07/2016</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,7 +8487,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>45889751</t>
+          <t>81479896</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8497,30 +8497,30 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ARZAPALO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>KARINA ROSMERY</t>
+          <t>ELIAS</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>02/12/1984</t>
+          <t>13/07/2009</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>21/07/2016</t>
+          <t>03/05/2018</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,7 +8550,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>81479896</t>
+          <t>31636156</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ELIAS</t>
+          <t>MAURO</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,16 +8574,16 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>13/07/2009</t>
+          <t>03/11/1931</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>03/05/2018</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>31636156</t>
+          <t>60203462</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8623,30 +8623,30 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MISIYAURI</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MAURO</t>
+          <t>ELIZABETH ELIZA</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>03/11/1931</t>
+          <t>27/03/2002</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,22 +8676,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>60203462</t>
+          <t>44219472</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SEGUIL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MISIYAURI</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ELIZABETH ELIZA</t>
+          <t>MATILDA PAULINA</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8700,16 +8700,16 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>27/03/2002</t>
+          <t>03/01/1964</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>10/05/2016</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,45 +8739,45 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>44219472</t>
+          <t>73972041</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SEGUIL</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>MATILDA PAULINA</t>
+          <t>JHAN PIERO</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>03/01/1964</t>
+          <t>02/10/2003</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>10/05/2016</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,22 +8802,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>73972041</t>
+          <t>46628784</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LEONARDO</t>
+          <t>VELASCO</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>JHAN PIERO</t>
+          <t>DELMER</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8826,16 +8826,16 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>02/10/2003</t>
+          <t>20/01/1990</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">

--- a/exports/488_san-andres.xlsx
+++ b/exports/488_san-andres.xlsx
@@ -4581,45 +4581,45 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20982401</t>
+          <t>60369313</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TEODORA</t>
+          <t>HERNAN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14/12/1962</t>
+          <t>18/12/2002</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>20/02/2012</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,45 +4644,45 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>43120883</t>
+          <t>20982401</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PERALES</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EDWIN IVAN</t>
+          <t>TEODORA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14/07/1985</t>
+          <t>14/12/1962</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>46240896</t>
+          <t>43120883</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>EDWIN IVAN</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4731,11 +4731,11 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14/09/1989</t>
+          <t>14/07/1985</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4770,22 +4770,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>40537496</t>
+          <t>46240896</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ESPEJO</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>PERALES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>JORGE LUIS</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4794,11 +4794,11 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>05/04/1979</t>
+          <t>14/09/1989</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,22 +4833,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>91930187</t>
+          <t>40537496</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>ESPEJO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OSORIO</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>JHAYR ALDAHIR ADRIEL</t>
+          <t>JORGE LUIS</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,16 +4857,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14/07/2020</t>
+          <t>05/04/1979</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20991423</t>
+          <t>73091283</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>ESPIRITU</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>APARICIO</t>
+          <t>RONALDO ROBERTO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>12/12/1966</t>
+          <t>06/08/1998</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>09/02/2015</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,22 +4959,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>61507200</t>
+          <t>91930187</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAINICELA</t>
+          <t>OSORIO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>JEFERSON FRANDUKS</t>
+          <t>JHAYR ALDAHIR ADRIEL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4983,16 +4983,16 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>18/04/2009</t>
+          <t>14/07/2020</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,45 +5022,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>61634660</t>
+          <t>20991423</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GUTARRA</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BRILLIT MAYELY</t>
+          <t>APARICIO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>03/01/2009</t>
+          <t>12/12/1966</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>09/02/2015</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,7 +5085,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>81479837</t>
+          <t>61634660</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5100,30 +5100,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BRAYAN SMITH</t>
+          <t>BRILLIT MAYELY</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>11/07/2015</t>
+          <t>03/01/2009</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>19/11/2015</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,7 +5148,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>41715866</t>
+          <t>81479837</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CARHUAMACA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VALENTIN</t>
+          <t>BRAYAN SMITH</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>12/06/1981</t>
+          <t>11/07/2015</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>21/07/2016</t>
+          <t>19/11/2015</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,22 +5211,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>77904813</t>
+          <t>41715866</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GUTARRA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>CARHUAMACA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VICTOR RODOLFO</t>
+          <t>VALENTIN</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>24/02/2001</t>
+          <t>12/06/1981</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>21/07/2016</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,22 +5274,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20962206</t>
+          <t>77904813</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>VICTOR RODOLFO</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>27/08/1946</t>
+          <t>24/02/2001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,22 +5337,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>47867880</t>
+          <t>20962206</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>JONAS</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5361,16 +5361,16 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>25/05/1992</t>
+          <t>27/08/1946</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>11/09/2020</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>77213330</t>
+          <t>47867880</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5415,20 +5415,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FLOR KELLY</t>
+          <t>JONAS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>26/06/1995</t>
+          <t>25/05/1992</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>21/08/2012</t>
+          <t>11/09/2020</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,7 +5463,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20047153</t>
+          <t>77213330</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5473,25 +5473,25 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>FLOR KELLY</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>08/12/1971</t>
+          <t>26/06/1995</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>24/05/2016</t>
+          <t>21/08/2012</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,35 +5526,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>80634083</t>
+          <t>20047153</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>INOCENTE</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PATRICIA MARGOT</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>27/10/1978</t>
+          <t>08/12/1971</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>24/05/2016</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>79213733</t>
+          <t>80634083</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LAPA</t>
+          <t>INOCENTE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>TAYRA DANNA</t>
+          <t>PATRICIA MARGOT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5613,21 +5613,21 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>28/05/2015</t>
+          <t>27/10/1978</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,22 +5652,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20420557</t>
+          <t>79213733</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LAUREANO</t>
+          <t>LAPA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MANTARI</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ELA MARCEA</t>
+          <t>TAYRA DANNA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5676,21 +5676,21 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>26/10/1965</t>
+          <t>28/05/2015</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>16/02/2022</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20990369</t>
+          <t>20420557</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>LAUREANO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CAYSAHUANA</t>
+          <t>MANTARI</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CATALINA</t>
+          <t>ELA MARCEA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,11 +5739,11 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>25/11/1949</t>
+          <t>26/10/1965</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>28/11/2014</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>48998854</t>
+          <t>20990369</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5788,25 +5788,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CAYSAHUANA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PEDRO PABLO</t>
+          <t>CATALINA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>29/06/1963</t>
+          <t>25/11/1949</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>14/09/2020</t>
+          <t>28/11/2014</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,35 +5841,35 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20968366</t>
+          <t>48998854</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LIMAS</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CAMPOS DE CAMARGO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TEOFILA</t>
+          <t>PEDRO PABLO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>02/09/1934</t>
+          <t>29/06/1963</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>01/09/2016</t>
+          <t>14/09/2020</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,45 +5904,45 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>46371234</t>
+          <t>20968366</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>LIMAS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CAMPOS DE CAMARGO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CEFERINO ARMANDO</t>
+          <t>TEOFILA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>23/02/1989</t>
+          <t>02/09/1934</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>01/09/2016</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,22 +5967,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>61697344</t>
+          <t>46371234</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MAGUIÑA</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>JHOVANY ROLY</t>
+          <t>CEFERINO ARMANDO</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5991,21 +5991,21 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>27/05/2010</t>
+          <t>23/02/1989</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,7 +6030,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>81479820</t>
+          <t>61697344</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6045,30 +6045,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MARIANA YOMARA</t>
+          <t>JHOVANY ROLY</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>29/03/2015</t>
+          <t>27/05/2010</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>29/05/2020</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,22 +6093,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>72178504</t>
+          <t>81479820</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>MAGUIÑA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KHERLY JOHANA</t>
+          <t>MARIANA YOMARA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,16 +6117,16 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>16/05/2000</t>
+          <t>29/03/2015</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>29/05/2020</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,45 +6156,45 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>73668062</t>
+          <t>72178504</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MARAVI</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VALTOP</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>HILSER ELMER</t>
+          <t>KHERLY JOHANA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>14/05/1994</t>
+          <t>16/05/2000</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>27/11/2020</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>45045846</t>
+          <t>73668062</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MARAVI</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>VALTOP</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>OSCAR BENITO</t>
+          <t>HILSER ELMER</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6243,11 +6243,11 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23/02/1988</t>
+          <t>14/05/1994</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>27/11/2020</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,7 +6282,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>80349247</t>
+          <t>45045846</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NOE ISAIAS</t>
+          <t>OSCAR BENITO</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6306,11 +6306,11 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>21/07/1979</t>
+          <t>23/02/1988</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,22 +6345,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>48484599</t>
+          <t>80349247</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MOYA</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DAVID ANGEL</t>
+          <t>NOE ISAIAS</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6369,11 +6369,11 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>16/01/1994</t>
+          <t>21/07/1979</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>28/03/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,7 +6408,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>46967694</t>
+          <t>48484599</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6418,25 +6418,25 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LUCIANA SUSANA</t>
+          <t>DAVID ANGEL</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>30/05/1991</t>
+          <t>16/01/1994</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>04/05/2012</t>
+          <t>28/03/2013</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,7 +6471,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>48759111</t>
+          <t>46967694</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EDITH</t>
+          <t>LUCIANA SUSANA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6495,11 +6495,11 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>09/10/1995</t>
+          <t>30/05/1991</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>19/08/2015</t>
+          <t>04/05/2012</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>73668026</t>
+          <t>48759111</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PALACIOS</t>
+          <t>MOYA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ZANDRA KARINA</t>
+          <t>EDITH</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>18/09/1997</t>
+          <t>09/10/1995</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>19/03/2024</t>
+          <t>19/08/2015</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,7 +6597,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>21013692</t>
+          <t>73668026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6607,35 +6607,35 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PORTOCARRERO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>MARIO</t>
+          <t>ZANDRA KARINA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>13/11/1977</t>
+          <t>18/09/1997</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>19/03/2024</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,7 +6660,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20998003</t>
+          <t>21013692</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SALOME</t>
+          <t>PORTOCARRERO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>TEODORO</t>
+          <t>MARIO</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6684,16 +6684,16 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>03/09/1965</t>
+          <t>13/11/1977</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6723,22 +6723,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>60369342</t>
+          <t>20998003</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>PALACIOS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>YAMIR FERNANDO</t>
+          <t>TEODORO</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,21 +6747,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>18/05/2008</t>
+          <t>03/09/1965</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,22 +6786,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>48638943</t>
+          <t>60369342</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PATIÑO</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AMERICO</t>
+          <t>YAMIR FERNANDO</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6810,21 +6810,21 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>22/10/1995</t>
+          <t>18/05/2008</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,45 +6849,45 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>61282644</t>
+          <t>48638943</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PAYANO</t>
+          <t>PATIÑO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LEVANO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ALEXANDRA CELINE</t>
+          <t>AMERICO</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>31/01/2008</t>
+          <t>22/10/1995</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,35 +6912,35 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>77145038</t>
+          <t>61282644</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>PAYANO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>LEVANO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EFRAIN LIZANDRO</t>
+          <t>ALEXANDRA CELINE</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>25/06/2000</t>
+          <t>31/01/2008</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,40 +6975,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>71957554</t>
+          <t>77145038</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MONTALGO</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NELY JHENY</t>
+          <t>EFRAIN LIZANDRO</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>18/10/1995</t>
+          <t>25/06/2000</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,35 +7038,35 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>48096106</t>
+          <t>71957554</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AVENIO</t>
+          <t>MONTALGO</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ALEX LENIN</t>
+          <t>NELY JHENY</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>24/01/1994</t>
+          <t>18/10/1995</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>05/12/2013</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,7 +7101,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>78212853</t>
+          <t>48096106</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7111,30 +7111,30 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>AVENIO</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DAYANA SAMIRA</t>
+          <t>ALEX LENIN</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>11/07/2013</t>
+          <t>24/01/1994</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7164,45 +7164,45 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>44931859</t>
+          <t>78212853</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>QUINTANILLA</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PARRAGA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>MARINO LORENZO</t>
+          <t>DAYANA SAMIRA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>21/07/1987</t>
+          <t>11/07/2013</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>21/05/2021</t>
+          <t>05/12/2013</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,22 +7227,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20994095</t>
+          <t>44931859</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUINTANILLA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ALIAGA</t>
+          <t>PARRAGA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>MARINO LORENZO</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7251,11 +7251,11 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>03/01/1971</t>
+          <t>21/07/1987</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>21/05/2021</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>42898832</t>
+          <t>20994095</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>ALIAGA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>MAXIMO JUAN</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>27/03/1985</t>
+          <t>03/01/1971</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>14/09/2020</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,7 +7353,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>48118279</t>
+          <t>42898832</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7363,25 +7363,25 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>CELIA</t>
+          <t>MAXIMO JUAN</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>05/08/1990</t>
+          <t>27/03/1985</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>14/09/2020</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,7 +7416,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>19963519</t>
+          <t>48118279</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PASTRANA</t>
+          <t>PARIACHI</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ANTONIA</t>
+          <t>CELIA</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,11 +7440,11 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>12/06/1968</t>
+          <t>05/08/1990</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>14/10/2016</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,35 +7479,35 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>47788809</t>
+          <t>19963519</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>PASTRANA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>BASILIO</t>
+          <t>ANTONIA</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>13/04/1993</t>
+          <t>12/06/1968</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>14/10/2016</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,45 +7542,45 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>20416033</t>
+          <t>47788809</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PAULINA</t>
+          <t>BASILIO</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>04/05/1956</t>
+          <t>13/04/1993</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,45 +7605,45 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>77498212</t>
+          <t>20416033</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>EMERSON WILLIAM</t>
+          <t>PAULINA</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>24/10/1998</t>
+          <t>04/05/1956</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,22 +7668,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>61697345</t>
+          <t>77498212</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ARTUR JHAIR</t>
+          <t>EMERSON WILLIAM</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,11 +7692,11 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>17/01/2008</t>
+          <t>24/10/1998</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,7 +7731,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>80846521</t>
+          <t>61697345</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DANILO JOSSAFAT</t>
+          <t>ARTUR JHAIR</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>13/09/2012</t>
+          <t>17/01/2008</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>05/07/2013</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,7 +7794,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>81479855</t>
+          <t>80846521</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7809,25 +7809,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ARELI TAMARA</t>
+          <t>DANILO JOSSAFAT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>15/10/2015</t>
+          <t>13/09/2012</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>19/04/2016</t>
+          <t>05/07/2013</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,7 +7857,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>93360444</t>
+          <t>81479855</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7872,20 +7872,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ABDIAS OTONIEL</t>
+          <t>ARELI TAMARA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>25/04/2023</t>
+          <t>15/10/2015</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>26/07/2023</t>
+          <t>19/04/2016</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,7 +7920,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>48893189</t>
+          <t>93360444</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>ABDIAS OTONIEL</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7944,21 +7944,21 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>17/07/1965</t>
+          <t>25/04/2023</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>27/10/2015</t>
+          <t>26/07/2023</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,7 +7983,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>80064918</t>
+          <t>48893189</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>MARCIAL</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8007,21 +8007,21 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>28/09/1977</t>
+          <t>17/07/1965</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>15/02/2012</t>
+          <t>27/10/2015</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,7 +8046,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>42797175</t>
+          <t>80064918</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SAMUEL</t>
+          <t>MARCIAL</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8070,11 +8070,11 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>06/12/1984</t>
+          <t>28/09/1977</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>10/05/2016</t>
+          <t>15/02/2012</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,22 +8109,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>46811206</t>
+          <t>42797175</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>POMA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>CUPERTINO</t>
+          <t>SAMUEL</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8133,11 +8133,11 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>31/12/1981</t>
+          <t>06/12/1984</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>10/05/2016</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,45 +8172,45 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>61055413</t>
+          <t>46811206</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RONCAL</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>POMA</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>MARIANGELA</t>
+          <t>CUPERTINO</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>05/06/2007</t>
+          <t>31/12/1981</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>07/02/2023</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,22 +8235,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>19959000</t>
+          <t>61055413</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>RONCAL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ANA BRIGIDA</t>
+          <t>MARIANGELA</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8259,21 +8259,21 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>01/02/1961</t>
+          <t>05/06/2007</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>27/07/2016</t>
+          <t>07/02/2023</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>20997885</t>
+          <t>19959000</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SALOME</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ADELAIDA GENOVEBA</t>
+          <t>ANA BRIGIDA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,11 +8322,11 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>30/11/1956</t>
+          <t>01/02/1961</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>27/07/2016</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,22 +8361,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>47441568</t>
+          <t>20997885</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SALVATIERRA</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>HUAYRA</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>PAULINA</t>
+          <t>ADELAIDA GENOVEBA</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8385,21 +8385,21 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>22/06/1986</t>
+          <t>30/11/1956</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>08/02/2012</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,22 +8424,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>45889751</t>
+          <t>47441568</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SALVATIERRA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ARZAPALO</t>
+          <t>HUAYRA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>KARINA ROSMERY</t>
+          <t>PAULINA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8448,11 +8448,11 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>02/12/1984</t>
+          <t>22/06/1986</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>21/07/2016</t>
+          <t>08/02/2012</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,7 +8487,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>81479896</t>
+          <t>45889751</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8497,30 +8497,30 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>ARZAPALO</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ELIAS</t>
+          <t>KARINA ROSMERY</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>13/07/2009</t>
+          <t>02/12/1984</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>03/05/2018</t>
+          <t>21/07/2016</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,7 +8550,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>31636156</t>
+          <t>81479896</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>MAURO</t>
+          <t>ELIAS</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,16 +8574,16 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>03/11/1931</t>
+          <t>13/07/2009</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>03/05/2018</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>60203462</t>
+          <t>31636156</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8623,30 +8623,30 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MISIYAURI</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ELIZABETH ELIZA</t>
+          <t>MAURO</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>27/03/2002</t>
+          <t>03/11/1931</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,22 +8676,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>44219472</t>
+          <t>60203462</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SEGUIL</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>MISIYAURI</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>MATILDA PAULINA</t>
+          <t>ELIZABETH ELIZA</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8700,16 +8700,16 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>03/01/1964</t>
+          <t>27/03/2002</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>10/05/2016</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,45 +8739,45 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>73972041</t>
+          <t>44219472</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>SEGUIL</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LEONARDO</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>JHAN PIERO</t>
+          <t>MATILDA PAULINA</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>02/10/2003</t>
+          <t>03/01/1964</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>10/05/2016</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,22 +8802,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>46628784</t>
+          <t>73972041</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VELASCO</t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DELMER</t>
+          <t>JHAN PIERO</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8826,16 +8826,16 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20/01/1990</t>
+          <t>02/10/2003</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">

--- a/exports/488_san-andres.xlsx
+++ b/exports/488_san-andres.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11/02/2013</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09/04/2024</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3510,40 +3510,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>80846543</t>
+          <t>43113757</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CHAMORRO</t>
+          <t>CAVERO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>JULCARIMA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ANGIE MARYORY</t>
+          <t>RICHARD EDWIN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14/01/2013</t>
+          <t>22/08/1985</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>23/09/2013</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>44753194</t>
+          <t>80846543</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3583,35 +3583,35 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LAURA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FIDEL</t>
+          <t>ANGIE MARYORY</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>17/11/1985</t>
+          <t>14/01/2013</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17/07/2021</t>
+          <t>23/09/2013</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,45 +3636,45 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20968327</t>
+          <t>44753194</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>CHAMORRO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DE REYES</t>
+          <t>LAURA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JACINTA</t>
+          <t>FIDEL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28/04/1947</t>
+          <t>17/11/1985</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>24/05/2016</t>
+          <t>17/07/2021</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,45 +3699,45 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>60551875</t>
+          <t>20968327</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CHUJUTALLI</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>APUELA</t>
+          <t>DE REYES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GINO LUIS</t>
+          <t>JACINTA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>09/05/2002</t>
+          <t>28/04/1947</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>24/05/2016</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,22 +3762,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>42350602</t>
+          <t>60551875</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>CHUJUTALLI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>APUELA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RICHARD HENRI</t>
+          <t>GINO LUIS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3786,21 +3786,21 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>12/03/1984</t>
+          <t>09/05/2002</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>08/02/2012</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>75645579</t>
+          <t>42350602</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3835,30 +3835,30 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SALVATIERRA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LUZ ESTRELLA</t>
+          <t>RICHARD HENRI</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>25/01/2011</t>
+          <t>12/03/1984</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>63152270</t>
+          <t>75645579</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>YERALIN MEDALY</t>
+          <t>LUZ ESTRELLA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>25/02/2012</t>
+          <t>25/01/2011</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>17/07/2012</t>
+          <t>08/02/2012</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>47412260</t>
+          <t>63152270</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DE LA O</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ARCA</t>
+          <t>SALVATIERRA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ELSA MIRELLA</t>
+          <t>YERALIN MEDALY</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,16 +3975,16 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>23/10/1992</t>
+          <t>25/02/2012</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>19/10/2012</t>
+          <t>17/07/2012</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,35 +4014,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>45031299</t>
+          <t>47412260</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DELACRUZ</t>
+          <t>DE LA O</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>ARCA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>GLICERIO</t>
+          <t>ELSA MIRELLA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14/08/1986</t>
+          <t>23/10/1992</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>19/10/2012</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,22 +4077,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>44503913</t>
+          <t>45031299</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DELAO</t>
+          <t>DELACRUZ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PAEZ</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ALEX ELIAS</t>
+          <t>GLICERIO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4101,11 +4101,11 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>05/12/1982</t>
+          <t>14/08/1986</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>10/05/2016</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,22 +4140,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>77030422</t>
+          <t>44503913</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>DELAO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>PAEZ</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EFRAIN YAMPIRE</t>
+          <t>ALEX ELIAS</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4164,21 +4164,21 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>30/08/2002</t>
+          <t>05/12/1982</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>23/05/2018</t>
+          <t>10/05/2016</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>62188604</t>
+          <t>77030422</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4218,25 +4218,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ISABEL SANDRA</t>
+          <t>EFRAIN YAMPIRE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>25/06/2010</t>
+          <t>30/08/2002</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>23/05/2018</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,7 +4266,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>45072784</t>
+          <t>62188604</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4276,35 +4276,35 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t>ISABEL SANDRA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>10/02/1987</t>
+          <t>25/06/2010</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31/05/2021</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20439774</t>
+          <t>45072784</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>INDALECIO EFRAIN</t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4353,11 +4353,11 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>16/06/1976</t>
+          <t>10/02/1987</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>13/09/2017</t>
+          <t>31/05/2021</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,7 +4392,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>45734910</t>
+          <t>20439774</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>GOMERCINDO ADALBERTO</t>
+          <t>INDALECIO EFRAIN</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4416,11 +4416,11 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>28/09/1980</t>
+          <t>16/06/1976</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>21/07/2016</t>
+          <t>13/09/2017</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>48301880</t>
+          <t>45734910</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4470,20 +4470,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>IRAIDA YULISA</t>
+          <t>GOMERCINDO ADALBERTO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20/01/1993</t>
+          <t>28/09/1980</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>30/08/2018</t>
+          <t>21/07/2016</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,7 +4518,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>77077788</t>
+          <t>48301880</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MARYMAR EVELIN</t>
+          <t>IRAIDA YULISA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4542,11 +4542,11 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20/01/1996</t>
+          <t>20/01/1993</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>20/02/2012</t>
+          <t>30/08/2018</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,22 +4581,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20982401</t>
+          <t>77077788</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TEODORA</t>
+          <t>MARYMAR EVELIN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14/12/1962</t>
+          <t>20/01/1996</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>28/06/2011</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,45 +4644,45 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>43120883</t>
+          <t>20982401</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PERALES</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EDWIN IVAN</t>
+          <t>TEODORA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14/07/1985</t>
+          <t>14/12/1962</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>28/06/2011</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>46240896</t>
+          <t>43120883</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t>EDWIN IVAN</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4731,11 +4731,11 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14/09/1989</t>
+          <t>14/07/1985</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4770,22 +4770,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>40537496</t>
+          <t>46240896</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ESPEJO</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>PERALES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>JORGE LUIS</t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4794,11 +4794,11 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>05/04/1979</t>
+          <t>14/09/1989</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,22 +4833,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>91930187</t>
+          <t>40537496</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>ESPEJO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OSORIO</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>JHAYR ALDAHIR ADRIEL</t>
+          <t>JORGE LUIS</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,16 +4857,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14/07/2020</t>
+          <t>05/04/1979</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20991423</t>
+          <t>91930187</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>OSORIO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>APARICIO</t>
+          <t>JHAYR ALDAHIR ADRIEL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>12/12/1966</t>
+          <t>14/07/2020</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>09/02/2015</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,22 +4959,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>61507200</t>
+          <t>79647143</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAINICELA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>JEFERSON FRANDUKS</t>
+          <t>ESTEFANO ADEMAR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4983,16 +4983,16 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>18/04/2009</t>
+          <t>27/04/2016</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,45 +5022,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>61634660</t>
+          <t>20991423</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GUTARRA</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BRILLIT MAYELY</t>
+          <t>APARICIO</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>03/01/2009</t>
+          <t>12/12/1966</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>09/02/2015</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,22 +5085,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>81479837</t>
+          <t>61507200</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GUTARRA</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CAINICELA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BRAYAN SMITH</t>
+          <t>JEFERSON FRANDUKS</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5109,21 +5109,21 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>11/07/2015</t>
+          <t>18/04/2009</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>19/11/2015</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,7 +5148,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>41715866</t>
+          <t>61634660</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5158,35 +5158,35 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CARHUAMACA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VALENTIN</t>
+          <t>BRILLIT MAYELY</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>12/06/1981</t>
+          <t>03/01/2009</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>21/07/2016</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,22 +5211,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>77904813</t>
+          <t>81479837</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GUTARRA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VICTOR RODOLFO</t>
+          <t>BRAYAN SMITH</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>24/02/2001</t>
+          <t>11/07/2015</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/11/2015</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,22 +5274,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20962206</t>
+          <t>41715866</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>GUTARRA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>CARHUAMACA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>VALENTIN</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5298,16 +5298,16 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>27/08/1946</t>
+          <t>12/06/1981</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>21/07/2016</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,22 +5337,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>47867880</t>
+          <t>77904813</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>JONAS</t>
+          <t>VICTOR RODOLFO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5361,21 +5361,21 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>25/05/1992</t>
+          <t>24/02/2001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>11/09/2020</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,40 +5400,40 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>77213330</t>
+          <t>20962206</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FLOR KELLY</t>
+          <t>JOSE</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>26/06/1995</t>
+          <t>27/08/1946</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>21/08/2012</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,45 +5463,45 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20047153</t>
+          <t>73660239</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GASPAR</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>EDITH YANETH</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>08/12/1971</t>
+          <t>18/06/1998</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>24/05/2016</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,35 +5526,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>80634083</t>
+          <t>47867880</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>INOCENTE</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CISNEROS</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PATRICIA MARGOT</t>
+          <t>JONAS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>27/10/1978</t>
+          <t>25/05/1992</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>11/09/2020</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>79213733</t>
+          <t>77213330</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LAPA</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>TAYRA DANNA</t>
+          <t>FLOR KELLY</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5613,21 +5613,21 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>28/05/2015</t>
+          <t>26/06/1995</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>16/02/2022</t>
+          <t>21/08/2012</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,45 +5652,45 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20420557</t>
+          <t>20047153</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LAUREANO</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MANTARI</t>
+          <t>GASPAR</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ELA MARCEA</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>26/10/1965</t>
+          <t>08/12/1971</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>24/05/2016</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,22 +5715,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20990369</t>
+          <t>80634083</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>INOCENTE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CAYSAHUANA</t>
+          <t>CISNEROS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CATALINA</t>
+          <t>PATRICIA MARGOT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5739,16 +5739,16 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>25/11/1949</t>
+          <t>27/10/1978</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>28/11/2014</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,45 +5778,45 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>48998854</t>
+          <t>79213733</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LAZARO</t>
+          <t>LAPA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PEDRO PABLO</t>
+          <t>TAYRA DANNA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>29/06/1963</t>
+          <t>28/05/2015</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>14/09/2020</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,22 +5841,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20968366</t>
+          <t>20420557</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LIMAS</t>
+          <t>LAUREANO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CAMPOS DE CAMARGO</t>
+          <t>MANTARI</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TEOFILA</t>
+          <t>ELA MARCEA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5865,11 +5865,11 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>02/09/1934</t>
+          <t>26/10/1965</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>01/09/2016</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,45 +5904,45 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>46371234</t>
+          <t>20990369</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CAYSAHUANA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CEFERINO ARMANDO</t>
+          <t>CATALINA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>23/02/1989</t>
+          <t>25/11/1949</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>28/11/2014</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,22 +5967,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>61697344</t>
+          <t>48998854</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MAGUIÑA</t>
+          <t>LAZARO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>JHOVANY ROLY</t>
+          <t>PEDRO PABLO</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5991,21 +5991,21 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>27/05/2010</t>
+          <t>29/06/1963</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>10/03/2014</t>
+          <t>14/09/2020</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,22 +6030,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>81479820</t>
+          <t>20968366</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MAGUIÑA</t>
+          <t>LIMAS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>CAMPOS DE CAMARGO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MARIANA YOMARA</t>
+          <t>TEOFILA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6054,21 +6054,21 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>29/03/2015</t>
+          <t>02/09/1934</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>29/05/2020</t>
+          <t>01/09/2016</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,45 +6093,45 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>72178504</t>
+          <t>46371234</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MANRIQUE</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TAPIA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KHERLY JOHANA</t>
+          <t>CEFERINO ARMANDO</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>16/05/2000</t>
+          <t>23/02/1989</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,22 +6156,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>73668062</t>
+          <t>73307893</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MARAVI</t>
+          <t>LUCERO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VALTOP</t>
+          <t>CLEMENTE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>HILSER ELMER</t>
+          <t>CLINTON</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6180,16 +6180,16 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>14/05/1994</t>
+          <t>21/04/2000</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>27/11/2020</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>45045846</t>
+          <t>61697344</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MAGUIÑA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>OSCAR BENITO</t>
+          <t>JHOVANY ROLY</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6243,21 +6243,21 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23/02/1988</t>
+          <t>27/05/2010</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>10/03/2014</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,45 +6282,45 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>80349247</t>
+          <t>81479820</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>MAGUIÑA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NOE ISAIAS</t>
+          <t>MARIANA YOMARA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>21/07/1979</t>
+          <t>29/03/2015</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>29/05/2020</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,45 +6345,45 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>48484599</t>
+          <t>72178504</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MOYA</t>
+          <t>MANRIQUE</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CURO</t>
+          <t>TAPIA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DAVID ANGEL</t>
+          <t>KHERLY JOHANA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>16/01/1994</t>
+          <t>16/05/2000</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>28/03/2013</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,35 +6408,35 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>46967694</t>
+          <t>45045846</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MOYA</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LUCIANA SUSANA</t>
+          <t>OSCAR BENITO</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>30/05/1991</t>
+          <t>23/02/1988</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>04/05/2012</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,35 +6471,35 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>48759111</t>
+          <t>80349247</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MOYA</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EDITH</t>
+          <t>NOE ISAIAS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>09/10/1995</t>
+          <t>21/07/1979</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>19/08/2015</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,45 +6534,45 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>73668026</t>
+          <t>48484599</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PALACIOS</t>
+          <t>MOYA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CURO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ZANDRA KARINA</t>
+          <t>DAVID ANGEL</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>18/09/1997</t>
+          <t>16/01/1994</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>19/03/2024</t>
+          <t>28/03/2013</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,35 +6597,35 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>21013692</t>
+          <t>46967694</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PALACIOS</t>
+          <t>MOYA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PORTOCARRERO</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>MARIO</t>
+          <t>LUCIANA SUSANA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>13/11/1977</t>
+          <t>30/05/1991</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>04/05/2012</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,40 +6660,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>20998003</t>
+          <t>48759111</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PALACIOS</t>
+          <t>MOYA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SALOME</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>TEODORO</t>
+          <t>EDITH</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>03/09/1965</t>
+          <t>09/10/1995</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,35 +6723,35 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>60369342</t>
+          <t>73668026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>PALACIOS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>YAMIR FERNANDO</t>
+          <t>ZANDRA KARINA</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>18/05/2008</t>
+          <t>18/09/1997</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/03/2024</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,22 +6786,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>48638943</t>
+          <t>21013692</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PATIÑO</t>
+          <t>PALACIOS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PORTOCARRERO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AMERICO</t>
+          <t>MARIO</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>22/10/1995</t>
+          <t>13/11/1977</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6849,45 +6849,45 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>61282644</t>
+          <t>20998003</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PAYANO</t>
+          <t>PALACIOS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LEVANO</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ALEXANDRA CELINE</t>
+          <t>TEODORO</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>31/01/2008</t>
+          <t>03/09/1965</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>77145038</t>
+          <t>60369342</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EFRAIN LIZANDRO</t>
+          <t>YAMIR FERNANDO</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,11 +6936,11 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>25/06/2000</t>
+          <t>18/05/2008</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,35 +6975,35 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>71957554</t>
+          <t>21014141</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>PASTRANA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MONTALGO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NELY JHENY</t>
+          <t>FREDY FULGENCIO</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>18/10/1995</t>
+          <t>28/10/1971</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,22 +7038,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>48096106</t>
+          <t>48638943</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>PATIÑO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AVENIO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ALEX LENIN</t>
+          <t>AMERICO</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7062,11 +7062,11 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>24/01/1994</t>
+          <t>22/10/1995</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>05/12/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,22 +7101,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>78212853</t>
+          <t>61282644</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>PAYANO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>LEVANO</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DAYANA SAMIRA</t>
+          <t>ALEXANDRA CELINE</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,21 +7125,21 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>11/07/2013</t>
+          <t>31/01/2008</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>05/12/2013</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,22 +7164,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>44931859</t>
+          <t>77145038</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>QUINTANILLA</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PARRAGA</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>MARINO LORENZO</t>
+          <t>EFRAIN LIZANDRO</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7188,16 +7188,16 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>21/07/1987</t>
+          <t>25/06/2000</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>21/05/2021</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,35 +7227,35 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20994095</t>
+          <t>71957554</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ALIAGA</t>
+          <t>MONTALGO</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>NELY JHENY</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>03/01/1971</t>
+          <t>18/10/1995</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,22 +7290,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>42898832</t>
+          <t>48096106</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>AVENIO</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>MAXIMO JUAN</t>
+          <t>ALEX LENIN</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>27/03/1985</t>
+          <t>24/01/1994</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>14/09/2020</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,22 +7353,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>48118279</t>
+          <t>78212853</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PARIACHI</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>CELIA</t>
+          <t>DAYANA SAMIRA</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7377,16 +7377,16 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>05/08/1990</t>
+          <t>11/07/2013</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,35 +7416,35 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>19963519</t>
+          <t>44931859</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>QUINTANILLA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PASTRANA</t>
+          <t>PARRAGA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ANTONIA</t>
+          <t>MARINO LORENZO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>12/06/1968</t>
+          <t>21/07/1987</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>14/10/2016</t>
+          <t>21/05/2021</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,22 +7479,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>47788809</t>
+          <t>20994095</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BENITO</t>
+          <t>ALIAGA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>BASILIO</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7503,11 +7503,11 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>13/04/1993</t>
+          <t>03/01/1971</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,45 +7542,45 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>20416033</t>
+          <t>42898832</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PAULINA</t>
+          <t>MAXIMO JUAN</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>04/05/1956</t>
+          <t>27/03/1985</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>14/09/2020</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,45 +7605,45 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>77498212</t>
+          <t>19963519</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>PASTRANA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>EMERSON WILLIAM</t>
+          <t>ANTONIA</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>24/10/1998</t>
+          <t>12/06/1968</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>26/12/2024</t>
+          <t>14/10/2016</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,22 +7668,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>61697345</t>
+          <t>47788809</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>BENITO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ARTUR JHAIR</t>
+          <t>BASILIO</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,21 +7692,21 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>17/01/2008</t>
+          <t>13/04/1993</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,45 +7731,45 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>80846521</t>
+          <t>20416033</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DANILO JOSSAFAT</t>
+          <t>PAULINA</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>13/09/2012</t>
+          <t>04/05/1956</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>05/07/2013</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,45 +7794,45 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>81479855</t>
+          <t>77498212</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ARELI TAMARA</t>
+          <t>EMERSON WILLIAM</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>15/10/2015</t>
+          <t>24/10/1998</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>19/04/2016</t>
+          <t>26/12/2024</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,7 +7857,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>93360444</t>
+          <t>61697345</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ABDIAS OTONIEL</t>
+          <t>ARTUR JHAIR</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7881,21 +7881,21 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>25/04/2023</t>
+          <t>17/01/2008</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>26/07/2023</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,7 +7920,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>48893189</t>
+          <t>80846521</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>DANILO JOSSAFAT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7944,21 +7944,21 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>17/07/1965</t>
+          <t>13/09/2012</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>27/10/2015</t>
+          <t>05/07/2013</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,7 +7983,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>80064918</t>
+          <t>81479855</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7993,35 +7993,35 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>MARCIAL</t>
+          <t>ARELI TAMARA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>28/09/1977</t>
+          <t>15/10/2015</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>15/02/2012</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,7 +8046,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>42797175</t>
+          <t>93360444</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>SAMUEL</t>
+          <t>ABDIAS OTONIEL</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>06/12/1984</t>
+          <t>25/04/2023</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>10/05/2016</t>
+          <t>26/07/2023</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,22 +8109,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>46811206</t>
+          <t>48893189</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>POMA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>CUPERTINO</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8133,21 +8133,21 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>31/12/1981</t>
+          <t>17/07/1965</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>27/10/2015</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,45 +8172,45 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>61055413</t>
+          <t>80064918</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RONCAL</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>MARIANGELA</t>
+          <t>MARCIAL</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>05/06/2007</t>
+          <t>28/09/1977</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>07/02/2023</t>
+          <t>15/02/2012</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,40 +8235,40 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>19959000</t>
+          <t>42797175</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ANA BRIGIDA</t>
+          <t>SAMUEL</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>01/02/1961</t>
+          <t>06/12/1984</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>27/07/2016</t>
+          <t>10/05/2016</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,45 +8298,45 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>20997885</t>
+          <t>46811206</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SALOME</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TOVAR</t>
+          <t>POMA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ADELAIDA GENOVEBA</t>
+          <t>CUPERTINO</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>30/11/1956</t>
+          <t>31/12/1981</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,22 +8361,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>47441568</t>
+          <t>61055413</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SALVATIERRA</t>
+          <t>RONCAL</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>HUAYRA</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>PAULINA</t>
+          <t>MARIANGELA</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8385,21 +8385,21 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>22/06/1986</t>
+          <t>05/06/2007</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>08/02/2012</t>
+          <t>07/02/2023</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,22 +8424,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>45889751</t>
+          <t>19959000</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ARZAPALO</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>KARINA ROSMERY</t>
+          <t>ANA BRIGIDA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8448,16 +8448,16 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>02/12/1984</t>
+          <t>01/02/1961</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>21/07/2016</t>
+          <t>27/07/2016</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,45 +8487,45 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>81479896</t>
+          <t>20997885</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SALOME</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>TOVAR</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ELIAS</t>
+          <t>ADELAIDA GENOVEBA</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>13/07/2009</t>
+          <t>30/11/1956</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>03/05/2018</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,40 +8550,40 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>31636156</t>
+          <t>47441568</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SALVATIERRA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>HUAYRA</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>MAURO</t>
+          <t>PAULINA</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>03/11/1931</t>
+          <t>22/06/1986</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>08/02/2012</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>60203462</t>
+          <t>45889751</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MISIYAURI</t>
+          <t>ARZAPALO</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ELIZABETH ELIZA</t>
+          <t>KARINA ROSMERY</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8637,16 +8637,16 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>27/03/2002</t>
+          <t>02/12/1984</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>21/07/2016</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,40 +8676,40 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>44219472</t>
+          <t>81479896</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SEGUIL</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>MATILDA PAULINA</t>
+          <t>ELIAS</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>03/01/1964</t>
+          <t>13/07/2009</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>10/05/2016</t>
+          <t>03/05/2018</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,22 +8739,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>73972041</t>
+          <t>31636156</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LEONARDO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>JHAN PIERO</t>
+          <t>MAURO</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8763,21 +8763,21 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>02/10/2003</t>
+          <t>03/11/1931</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,45 +8802,45 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>46628784</t>
+          <t>60203462</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VELASCO</t>
+          <t>MISIYAURI</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DELMER</t>
+          <t>ELIZABETH ELIZA</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20/01/1990</t>
+          <t>27/03/2002</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,22 +8865,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>92021439</t>
+          <t>44219472</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>SEGUIL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MADUEÑO</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>MARIA LUIZA MISHELL</t>
+          <t>MATILDA PAULINA</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8889,21 +8889,21 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>18/09/2020</t>
+          <t>03/01/1964</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>10/05/2016</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,45 +8928,45 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>20968518</t>
+          <t>73972041</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TELLO</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VDA DE SANCHEZ</t>
+          <t>LEONARDO</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ROLINDA</t>
+          <t>JHAN PIERO</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>14/08/1956</t>
+          <t>02/10/2003</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8991,22 +8991,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>20661308</t>
+          <t>46628784</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TENICELA</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CANCHAYA</t>
+          <t>VELASCO</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ASCENCIO GEREMIAS</t>
+          <t>DELMER</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9015,21 +9015,21 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>09/04/1958</t>
+          <t>20/01/1990</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>27/07/2016</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9054,22 +9054,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>48302100</t>
+          <t>92021439</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TORPOCO</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>POVIS</t>
+          <t>MADUEÑO</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LUZMILA</t>
+          <t>MARIA LUIZA MISHELL</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9078,21 +9078,21 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20/02/1993</t>
+          <t>18/09/2020</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9117,22 +9117,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>78659722</t>
+          <t>20968518</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TORPOCO</t>
+          <t>TELLO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>VDA DE SANCHEZ</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AYSHA LYN MAY</t>
+          <t>ROLINDA</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9141,21 +9141,21 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>23/06/2014</t>
+          <t>14/08/1956</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9180,22 +9180,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>73389574</t>
+          <t>20661308</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TENICELA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LIMAS</t>
+          <t>CANCHAYA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>YERSON ANDRE</t>
+          <t>ASCENCIO GEREMIAS</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9204,21 +9204,21 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>06/01/2005</t>
+          <t>09/04/1958</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>27/07/2016</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9243,22 +9243,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>60010099</t>
+          <t>48302100</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>URBANO</t>
+          <t>TORPOCO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SALAS</t>
+          <t>POVIS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ALVINA</t>
+          <t>LUZMILA</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9267,82 +9267,86 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>08/01/1997</t>
+          <t>20/02/1993</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>21/03/2024</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M141" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>78659722</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TORPOCO</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SOTO</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>AYSHA LYN MAY</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>12</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>23/06/2014</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2.ADOLESCENTE</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
           <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>24/01/2020</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M141" t="n">
-        <v>120602</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr"/>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>VALVERDE</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>APOLINARIO</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>SILVINO</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F142" t="n">
-        <v>20</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>28/08/2006</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>3.JOVEN</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
-        </is>
-      </c>
       <c r="J142" t="inlineStr">
         <is>
           <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
@@ -9350,7 +9354,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9365,45 +9369,45 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>49001435</t>
+          <t>73389574</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>LIMAS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>MARY LUISA</t>
+          <t>YERSON ANDRE</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>19/01/1971</t>
+          <t>06/01/2005</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9413,7 +9417,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>18/12/2018</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9428,22 +9432,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>45511514</t>
+          <t>60010099</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>URBANO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LUPE NANCY</t>
+          <t>ALVINA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9452,21 +9456,21 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>19/12/1972</t>
+          <t>08/01/1997</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9476,7 +9480,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>22/11/2012</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9489,47 +9493,43 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>20997625</t>
-        </is>
-      </c>
+      <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>VELASCO</t>
+          <t>VALVERDE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>CATTY</t>
+          <t>SILVINO</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>23/07/1967</t>
+          <t>28/08/2006</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9554,35 +9554,35 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>47130014</t>
+          <t>49001435</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CORDOVA</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ANDY LUIS</t>
+          <t>MARY LUISA</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>09/05/1992</t>
+          <t>19/01/1971</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>27/10/2025</t>
+          <t>18/12/2018</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9617,45 +9617,45 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>60930308</t>
+          <t>45511514</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SEGUIL</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>MAYCOL JHEYSON</t>
+          <t>LUPE NANCY</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>11/12/2006</t>
+          <t>19/12/1972</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>22/11/2012</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9680,35 +9680,35 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>48219167</t>
+          <t>20997625</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>VELASCO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SIGUIL</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>PELAYO IVAN</t>
+          <t>CATTY</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>23/06/1993</t>
+          <t>23/07/1967</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9743,22 +9743,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>41848301</t>
+          <t>47130014</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>VERA</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>CORDOVA</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ANTONIO ELISEO</t>
+          <t>ANDY LUIS</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9767,11 +9767,11 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>13/06/1983</t>
+          <t>09/05/1992</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>27/10/2025</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9806,63 +9806,315 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>60930308</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>VELIZ</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SEGUIL</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>MAYCOL JHEYSON</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>19</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>11/12/2006</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>3.JOVEN</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>14/11/2013</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>48219167</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>VELIZ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SIGUIL</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>PELAYO IVAN</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>33</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>23/06/1993</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>30/09/2014</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>48531418</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>VELIZ</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SOTO</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SHOLIT LAURA</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>31</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>27/03/1995</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M152" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>41848301</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>VERA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ANTONIO ELISEO</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>43</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>13/06/1983</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>21/03/2024</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M153" t="n">
+        <v>120602</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>78360605</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>YNOCENTE</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>MARAVI</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>STIVEN</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F150" t="n">
-        <v>13</v>
-      </c>
-      <c r="G150" t="inlineStr">
+      <c r="F154" t="n">
+        <v>12</v>
+      </c>
+      <c r="G154" t="inlineStr">
         <is>
           <t>07/11/2013</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>2.ADOLESCENTE</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I154" t="inlineStr">
         <is>
           <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>06/03/2024</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>COVIRIALI</t>
-        </is>
-      </c>
-      <c r="M150" t="n">
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>COVIRIALI</t>
+        </is>
+      </c>
+      <c r="M154" t="n">
         <v>120602</v>
       </c>
     </row>
